--- a/output/pdf_financials_xlsx/UTWO.xlsx
+++ b/output/pdf_financials_xlsx/UTWO.xlsx
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.1025</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.871852</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.1025</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.871852</v>
       </c>
     </row>
     <row r="37">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
